--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22704575-EE73-4FDF-B2E6-646C83DDC571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E3A4D9-5016-4328-9F6C-7F0177CFCD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
   <si>
     <t>Tasks</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>AWS Glue job videos</t>
+  </si>
+  <si>
+    <t>Client code understanding</t>
+  </si>
+  <si>
+    <t>Project Work</t>
   </si>
 </sst>
 </file>
@@ -909,7 +915,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -1287,8 +1293,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="15">
+        <v>45678</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="16"/>
+      <c r="B53" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="16"/>
+      <c r="B54" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A52:A54"/>
     <mergeCell ref="A49:A50"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A7:A14"/>

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E3A4D9-5016-4328-9F6C-7F0177CFCD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF64E911-1C88-4CD0-A0B4-76719B22ED03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t>Tasks</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Project Work</t>
+  </si>
+  <si>
+    <t>Working on project task</t>
   </si>
 </sst>
 </file>
@@ -323,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -363,6 +366,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -1320,6 +1324,17 @@
       </c>
       <c r="C54" s="13" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="17">
+        <v>45679</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF64E911-1C88-4CD0-A0B4-76719B22ED03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BE2708-8FA7-4F46-8206-24A8107050A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>Tasks</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Working on project task</t>
+  </si>
+  <si>
+    <t>Project Task</t>
   </si>
 </sst>
 </file>
@@ -326,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -360,13 +363,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +684,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>45636</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -688,7 +695,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
@@ -697,7 +704,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
@@ -706,7 +713,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>45637</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -717,7 +724,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
@@ -726,7 +733,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
@@ -735,7 +742,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>45638</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -746,7 +753,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
@@ -755,7 +762,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="A13" s="16">
         <v>45642</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -766,7 +773,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
@@ -775,7 +782,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
@@ -784,7 +791,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>45643</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -795,7 +802,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
@@ -804,10 +811,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
+      <c r="A19" s="17"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <v>45644</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -818,7 +825,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -827,7 +834,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="15">
+      <c r="A23" s="16">
         <v>45649</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -838,7 +845,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
@@ -852,12 +859,12 @@
       <c r="C26" s="14"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="4"/>
       <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="4"/>
       <c r="C29" s="6"/>
     </row>
@@ -919,7 +926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -950,7 +957,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="16">
         <v>45660</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -961,7 +968,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
@@ -970,7 +977,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>45663</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -981,7 +988,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -990,7 +997,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
@@ -999,7 +1006,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
@@ -1008,7 +1015,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
@@ -1017,7 +1024,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
@@ -1026,7 +1033,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
@@ -1035,11 +1042,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="16">
         <v>45664</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1050,7 +1057,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -1059,7 +1066,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="4" t="s">
         <v>40</v>
       </c>
@@ -1068,11 +1075,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="15">
+      <c r="A21" s="16">
         <v>45665</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1083,7 +1090,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="4" t="s">
         <v>42</v>
       </c>
@@ -1092,7 +1099,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1101,7 +1108,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="4" t="s">
         <v>44</v>
       </c>
@@ -1110,7 +1117,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="4" t="s">
         <v>45</v>
       </c>
@@ -1119,7 +1126,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="15">
+      <c r="A27" s="16">
         <v>45666</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1130,7 +1137,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
+      <c r="A28" s="17"/>
       <c r="B28" s="4" t="s">
         <v>47</v>
       </c>
@@ -1139,7 +1146,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="4" t="s">
         <v>48</v>
       </c>
@@ -1148,7 +1155,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="15">
+      <c r="A31" s="16">
         <v>45667</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -1159,7 +1166,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
+      <c r="A32" s="17"/>
       <c r="B32" s="4" t="s">
         <v>51</v>
       </c>
@@ -1168,7 +1175,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="16"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="4" t="s">
         <v>50</v>
       </c>
@@ -1180,7 +1187,7 @@
       <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="15">
+      <c r="A35" s="16">
         <v>45671</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -1191,7 +1198,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
+      <c r="A36" s="17"/>
       <c r="B36" s="4" t="s">
         <v>53</v>
       </c>
@@ -1200,7 +1207,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="16">
         <v>45672</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -1211,7 +1218,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="16"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="4" t="s">
         <v>55</v>
       </c>
@@ -1220,7 +1227,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="15">
+      <c r="A41" s="16">
         <v>45673</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -1231,7 +1238,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="16"/>
+      <c r="A42" s="17"/>
       <c r="B42" s="4" t="s">
         <v>56</v>
       </c>
@@ -1240,7 +1247,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="16"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="4" t="s">
         <v>57</v>
       </c>
@@ -1249,7 +1256,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="15">
+      <c r="A45" s="16">
         <v>45674</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -1260,7 +1267,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="16"/>
+      <c r="A46" s="17"/>
       <c r="B46" s="4" t="s">
         <v>59</v>
       </c>
@@ -1269,7 +1276,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="16"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="4" t="s">
         <v>60</v>
       </c>
@@ -1278,7 +1285,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="15">
+      <c r="A49" s="16">
         <v>45677</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -1289,7 +1296,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="4" t="s">
         <v>62</v>
       </c>
@@ -1298,7 +1305,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="16">
         <v>45678</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -1309,7 +1316,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="16"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="4" t="s">
         <v>63</v>
       </c>
@@ -1318,7 +1325,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="16"/>
+      <c r="A54" s="17"/>
       <c r="B54" s="4" t="s">
         <v>64</v>
       </c>
@@ -1327,7 +1334,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="17">
+      <c r="A56" s="15">
         <v>45679</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -1336,6 +1343,23 @@
       <c r="C56" s="12" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="15">
+        <v>45680</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="19"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B61" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BE2708-8FA7-4F46-8206-24A8107050A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A996FF76-2DC8-4A6F-92DE-E248090D0B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
   <si>
     <t>Tasks</t>
   </si>
@@ -329,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,15 +364,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -684,7 +683,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="16">
+      <c r="A2" s="17">
         <v>45636</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -695,7 +694,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
+      <c r="A3" s="17"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
@@ -704,7 +703,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
@@ -713,7 +712,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="17">
         <v>45637</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -724,7 +723,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
@@ -733,7 +732,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
@@ -742,7 +741,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
+      <c r="A10" s="17">
         <v>45638</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -753,7 +752,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
@@ -762,7 +761,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
+      <c r="A13" s="17">
         <v>45642</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -773,7 +772,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
@@ -782,7 +781,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
@@ -791,7 +790,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
+      <c r="A17" s="17">
         <v>45643</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -802,7 +801,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
@@ -811,10 +810,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
+      <c r="A19" s="18"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
+      <c r="A20" s="17">
         <v>45644</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -825,7 +824,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -834,7 +833,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
+      <c r="A23" s="17">
         <v>45649</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -845,7 +844,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
@@ -859,12 +858,12 @@
       <c r="C26" s="14"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
+      <c r="A28" s="17"/>
       <c r="B28" s="4"/>
       <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="4"/>
       <c r="C29" s="6"/>
     </row>
@@ -926,7 +925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -957,7 +956,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="16">
+      <c r="A4" s="17">
         <v>45660</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -968,7 +967,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
@@ -977,7 +976,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
+      <c r="A7" s="17">
         <v>45663</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -988,7 +987,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -997,7 +996,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
@@ -1006,7 +1005,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
@@ -1015,7 +1014,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
@@ -1024,7 +1023,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
@@ -1033,7 +1032,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
@@ -1042,11 +1041,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
+      <c r="A16" s="17">
         <v>45664</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1057,7 +1056,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -1066,7 +1065,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="4" t="s">
         <v>40</v>
       </c>
@@ -1075,11 +1074,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
+      <c r="A21" s="17">
         <v>45665</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1090,7 +1089,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="4" t="s">
         <v>42</v>
       </c>
@@ -1099,7 +1098,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1108,7 +1107,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="4" t="s">
         <v>44</v>
       </c>
@@ -1117,7 +1116,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="4" t="s">
         <v>45</v>
       </c>
@@ -1126,7 +1125,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
+      <c r="A27" s="17">
         <v>45666</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1137,7 +1136,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="4" t="s">
         <v>47</v>
       </c>
@@ -1146,7 +1145,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="4" t="s">
         <v>48</v>
       </c>
@@ -1155,7 +1154,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
+      <c r="A31" s="17">
         <v>45667</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -1166,7 +1165,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="4" t="s">
         <v>51</v>
       </c>
@@ -1175,7 +1174,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="4" t="s">
         <v>50</v>
       </c>
@@ -1187,7 +1186,7 @@
       <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
+      <c r="A35" s="17">
         <v>45671</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -1198,7 +1197,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="4" t="s">
         <v>53</v>
       </c>
@@ -1207,7 +1206,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
+      <c r="A38" s="17">
         <v>45672</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -1218,7 +1217,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
+      <c r="A39" s="18"/>
       <c r="B39" s="4" t="s">
         <v>55</v>
       </c>
@@ -1227,7 +1226,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
+      <c r="A41" s="17">
         <v>45673</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -1238,7 +1237,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="17"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="4" t="s">
         <v>56</v>
       </c>
@@ -1247,7 +1246,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="4" t="s">
         <v>57</v>
       </c>
@@ -1256,7 +1255,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="16">
+      <c r="A45" s="17">
         <v>45674</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -1267,7 +1266,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="17"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="4" t="s">
         <v>59</v>
       </c>
@@ -1276,7 +1275,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="4" t="s">
         <v>60</v>
       </c>
@@ -1285,7 +1284,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="16">
+      <c r="A49" s="17">
         <v>45677</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -1296,7 +1295,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="16"/>
+      <c r="A50" s="17"/>
       <c r="B50" s="4" t="s">
         <v>62</v>
       </c>
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="16">
+      <c r="A52" s="17">
         <v>45678</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -1316,7 +1315,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="17"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="4" t="s">
         <v>63</v>
       </c>
@@ -1325,7 +1324,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="17"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="4" t="s">
         <v>64</v>
       </c>
@@ -1356,10 +1355,18 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="19"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B61" s="18"/>
+      <c r="B59" s="16"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="15">
+        <v>45681</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A996FF76-2DC8-4A6F-92DE-E248090D0B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB09BCB-AE42-4C2C-8E8C-01F72A572E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t>Tasks</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Project Task</t>
+  </si>
+  <si>
+    <t>Jenkins tutorial video(Basics)</t>
   </si>
 </sst>
 </file>
@@ -329,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -372,6 +375,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -925,7 +931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -1368,8 +1374,32 @@
         <v>11</v>
       </c>
     </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="19"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="17">
+        <v>45684</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="17"/>
+      <c r="B63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A62:A63"/>
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="A49:A50"/>
     <mergeCell ref="A4:A5"/>

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB09BCB-AE42-4C2C-8E8C-01F72A572E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45373D44-FB4F-4CF6-9A2D-57CB091FBAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
   <si>
     <t>Tasks</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Jenkins tutorial video(Basics)</t>
+  </si>
+  <si>
+    <t>SQL practice on TABLE CREATION, INSERT,UPDATE,RENAME,REMOVE,IN,AND ,OR,DROP and DELETE</t>
   </si>
 </sst>
 </file>
@@ -332,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -366,7 +369,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -375,9 +377,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +688,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="16">
         <v>45636</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -700,7 +699,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
@@ -709,7 +708,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
@@ -718,7 +717,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="16">
         <v>45637</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -729,7 +728,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
@@ -738,7 +737,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
@@ -747,7 +746,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
+      <c r="A10" s="16">
         <v>45638</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -758,7 +757,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
@@ -767,7 +766,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+      <c r="A13" s="16">
         <v>45642</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -778,7 +777,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
@@ -787,7 +786,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
@@ -796,7 +795,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+      <c r="A17" s="16">
         <v>45643</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -807,7 +806,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
@@ -816,10 +815,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
+      <c r="A19" s="17"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="A20" s="16">
         <v>45644</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -830,7 +829,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -839,7 +838,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="A23" s="16">
         <v>45649</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -850,7 +849,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
@@ -864,12 +863,12 @@
       <c r="C26" s="14"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="4"/>
       <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="4"/>
       <c r="C29" s="6"/>
     </row>
@@ -931,11 +930,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="58.77734375" customWidth="1"/>
+    <col min="2" max="2" width="103.109375" customWidth="1"/>
     <col min="3" max="3" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -962,7 +961,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
+      <c r="A4" s="16">
         <v>45660</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -973,7 +972,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
@@ -982,7 +981,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
+      <c r="A7" s="16">
         <v>45663</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -993,7 +992,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -1002,7 +1001,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
@@ -1011,7 +1010,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1019,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
@@ -1029,7 +1028,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1037,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
@@ -1047,11 +1046,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="16">
         <v>45664</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1062,7 +1061,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -1071,7 +1070,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="4" t="s">
         <v>40</v>
       </c>
@@ -1080,11 +1079,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
+      <c r="A21" s="16">
         <v>45665</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1095,7 +1094,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="4" t="s">
         <v>42</v>
       </c>
@@ -1104,7 +1103,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1113,7 +1112,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="4" t="s">
         <v>44</v>
       </c>
@@ -1122,7 +1121,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="4" t="s">
         <v>45</v>
       </c>
@@ -1131,7 +1130,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27" s="16">
         <v>45666</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1142,7 +1141,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
+      <c r="A28" s="17"/>
       <c r="B28" s="4" t="s">
         <v>47</v>
       </c>
@@ -1151,7 +1150,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="4" t="s">
         <v>48</v>
       </c>
@@ -1160,7 +1159,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="17">
+      <c r="A31" s="16">
         <v>45667</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -1171,7 +1170,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
+      <c r="A32" s="17"/>
       <c r="B32" s="4" t="s">
         <v>51</v>
       </c>
@@ -1180,7 +1179,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="4" t="s">
         <v>50</v>
       </c>
@@ -1192,7 +1191,7 @@
       <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="17">
+      <c r="A35" s="16">
         <v>45671</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -1203,7 +1202,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="18"/>
+      <c r="A36" s="17"/>
       <c r="B36" s="4" t="s">
         <v>53</v>
       </c>
@@ -1212,7 +1211,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="17">
+      <c r="A38" s="16">
         <v>45672</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -1223,7 +1222,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="18"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="4" t="s">
         <v>55</v>
       </c>
@@ -1232,7 +1231,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="17">
+      <c r="A41" s="16">
         <v>45673</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -1243,7 +1242,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="18"/>
+      <c r="A42" s="17"/>
       <c r="B42" s="4" t="s">
         <v>56</v>
       </c>
@@ -1252,7 +1251,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="18"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="4" t="s">
         <v>57</v>
       </c>
@@ -1261,7 +1260,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="17">
+      <c r="A45" s="16">
         <v>45674</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -1272,7 +1271,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="18"/>
+      <c r="A46" s="17"/>
       <c r="B46" s="4" t="s">
         <v>59</v>
       </c>
@@ -1281,7 +1280,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="18"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="4" t="s">
         <v>60</v>
       </c>
@@ -1290,7 +1289,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="17">
+      <c r="A49" s="16">
         <v>45677</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -1301,7 +1300,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="17"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="4" t="s">
         <v>62</v>
       </c>
@@ -1310,7 +1309,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="17">
+      <c r="A52" s="16">
         <v>45678</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -1321,7 +1320,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="18"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="4" t="s">
         <v>63</v>
       </c>
@@ -1330,7 +1329,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="18"/>
+      <c r="A54" s="17"/>
       <c r="B54" s="4" t="s">
         <v>64</v>
       </c>
@@ -1339,7 +1338,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="10">
         <v>45679</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -1350,7 +1349,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="10">
         <v>45680</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -1361,10 +1360,10 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="16"/>
+      <c r="B59" s="15"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="10">
         <v>45681</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -1375,10 +1374,10 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C61" s="19"/>
+      <c r="C61" s="15"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="17">
+      <c r="A62" s="16">
         <v>45684</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -1389,11 +1388,22 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="17"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C63" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="10">
+        <v>45685</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45373D44-FB4F-4CF6-9A2D-57CB091FBAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C3B1C7-596E-4F12-93BA-AA828085EC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
   <si>
     <t>Tasks</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>SQL practice on TABLE CREATION, INSERT,UPDATE,RENAME,REMOVE,IN,AND ,OR,DROP and DELETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project code of tms_main and tms_test understanding </t>
+  </si>
+  <si>
+    <t>Group discussion on Deepseek AI</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -1407,8 +1413,29 @@
         <v>11</v>
       </c>
     </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="16">
+        <v>45686</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="17"/>
+      <c r="B68" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A67:A68"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="A49:A50"/>

--- a/Daily_status_file.xlsx
+++ b/Daily_status_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91955\Desktop\Daily_Status\Daily_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C3B1C7-596E-4F12-93BA-AA828085EC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8020C43A-868A-4210-9636-140C37012C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="73">
   <si>
     <t>Tasks</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>Group discussion on Deepseek AI</t>
+  </si>
+  <si>
+    <t>SQL practise on Joins, Group by, Order by</t>
+  </si>
+  <si>
+    <t>Python practise on List, Tuple, Set, Dictionary, Dictionary Slicing, Creating multiple dictionaries</t>
   </si>
 </sst>
 </file>
@@ -936,7 +942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA8F8A6-0C1B-4EE9-A7F3-676925BC8A00}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -1433,8 +1439,29 @@
         <v>11</v>
       </c>
     </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="16">
+        <v>45692</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="17"/>
+      <c r="B71" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A70:A71"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A52:A54"/>
